--- a/InputData/indst/CtIEPpUESoS/Cost to Impl Eff Policy per Unit E Saved or Shifted.xlsx
+++ b/InputData/indst/CtIEPpUESoS/Cost to Impl Eff Policy per Unit E Saved or Shifted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\United States\us-eps\InputData\indst\CtIEPpUESoS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/indst/CtIEPpUESoS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEAEDC2E-6B42-4CB5-AFA1-775DD85ABCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A57538-0921-FB42-950D-8A037CA96C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11100" yWindow="1140" windowWidth="16605" windowHeight="15210" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -833,10 +833,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -860,18 +860,13 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -879,25 +874,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="9" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="9" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1"/>
@@ -916,12 +903,8 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -936,9 +919,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1118,9 +1098,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1158,9 +1138,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1193,26 +1173,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1245,26 +1208,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1439,18 +1385,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="81.7109375" customWidth="1"/>
-    <col min="4" max="4" width="56.140625" customWidth="1"/>
+    <col min="2" max="2" width="81.6640625" customWidth="1"/>
+    <col min="4" max="4" width="56.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1461,31 +1407,31 @@
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>2013</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="2">
         <v>2010</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1493,15 +1439,15 @@
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
         <v>166</v>
       </c>
@@ -1509,31 +1455,31 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>2011</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="2">
         <v>2009</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
@@ -1541,197 +1487,187 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>2011</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="25" t="s">
+    <row r="25" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
         <v>2020</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="25"/>
-    </row>
-    <row r="30" spans="2:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="2:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="2:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>2011</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
-    </row>
-    <row r="38" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="25" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>0.98699999999999999</v>
       </c>
       <c r="B57" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="26">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="21">
         <v>1.0549999999999999</v>
       </c>
-      <c r="B58" s="25" t="s">
+      <c r="B58" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="25" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1751,20 +1687,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1772,22 +1708,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -1795,12 +1731,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1814,7 +1750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1829,7 +1765,7 @@
         <v>0.36555607695917408</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1844,7 +1780,7 @@
         <v>0.49267566948958574</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1859,7 +1795,7 @@
         <v>0.61937990072656646</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
@@ -1870,26 +1806,26 @@
         <v>0.49253721572510872</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="10"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f>2.93*10^-4</f>
         <v>2.9300000000000002E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="8"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="16">
         <f>D14*A17</f>
         <v>1.4431340420745687E-4</v>
       </c>
@@ -1905,121 +1841,118 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="29.5" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="29.5" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="18">
         <f>2.4*10^15</f>
         <v>2400000000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="21"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="18"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>34</v>
       </c>
@@ -2028,7 +1961,7 @@
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>61</v>
       </c>
@@ -2042,61 +1975,60 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="5">
         <v>114</v>
       </c>
       <c r="C25" s="5">
         <v>22</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="15">
         <f>284*10^9</f>
         <v>284000000000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="15">
         <f>(C25/B25)*D25</f>
         <v>54807017543.85965</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="22"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="22"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="22"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="20"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="19">
         <f>E25/B4</f>
         <v>2.2836257309941521E-5</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="22"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="25"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="22"/>
-      <c r="G30" s="55"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="G30" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2107,419 +2039,143 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131020BD-F268-461F-B03F-7101039E9E7B}">
-  <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1">
         <v>2009</v>
       </c>
-      <c r="C1" s="25">
+      <c r="C1">
         <v>2010</v>
       </c>
-      <c r="D1" s="25">
+      <c r="D1">
         <v>2011</v>
       </c>
-      <c r="E1" s="25">
+      <c r="E1">
         <v>2012</v>
       </c>
-      <c r="F1" s="25">
+      <c r="F1">
         <v>2013</v>
       </c>
-      <c r="G1" s="25">
+      <c r="G1">
         <v>2014</v>
       </c>
-      <c r="H1" s="25">
+      <c r="H1">
         <v>2015</v>
       </c>
-      <c r="I1" s="25">
+      <c r="I1">
         <v>2016</v>
       </c>
-      <c r="J1" s="25">
+      <c r="J1">
         <v>2017</v>
       </c>
-      <c r="K1" s="25">
+      <c r="K1">
         <v>2018</v>
       </c>
-      <c r="L1" s="25">
+      <c r="L1">
         <v>2019</v>
       </c>
-      <c r="M1" s="25">
+      <c r="M1">
         <v>2020</v>
       </c>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="17">
         <f>NPV(0.07,B2:M2)</f>
         <v>79000000000.000015</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="17">
         <v>9946257103.7466221</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="17">
         <f>B2</f>
         <v>9946257103.7466221</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <f t="shared" ref="D2:M2" si="0">C2</f>
         <v>9946257103.7466221</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="M2" s="20">
+      <c r="M2" s="17">
         <f t="shared" si="0"/>
         <v>9946257103.7466221</v>
       </c>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3">
         <f>51+28</f>
         <v>79</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B4">
         <f>M4/COUNT(B1:M1)</f>
         <v>201.66666666666666</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25">
+      <c r="M4">
         <f>1550+870</f>
         <v>2420</v>
       </c>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="20">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B5" s="17">
         <f>B2/(B4*1000000000000)*Q5</f>
         <v>5.2772702980209352E-5</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25" t="s">
+      <c r="O5" t="s">
         <v>165</v>
       </c>
       <c r="Q5">
         <v>1.07</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2530,461 +2186,435 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-    </row>
-    <row r="6" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="23" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="24">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="25">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="26">
         <v>6.5242598122280206</v>
       </c>
-      <c r="D10" s="38"/>
-    </row>
-    <row r="11" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="D10" s="31"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="32">
         <v>6.3954140084752677E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="32">
         <v>52.826854199999993</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="27">
         <v>53860</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="27">
         <v>87540</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="25">
         <v>1</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="28">
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="29">
         <v>3.3475000000000001</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="29">
         <v>3.3475000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="30">
         <v>5280</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="30">
         <v>5280</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="30">
         <f>C18*C19</f>
         <v>17674.8</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="30">
         <f>D18*D19</f>
         <v>17674.8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="14"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>120</v>
       </c>
       <c r="B23" s="8"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="16">
         <f>C16/(C20*10^6)</f>
         <v>3.047276348247222E-6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="25"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="24">
         <v>25</v>
       </c>
-      <c r="D31" s="25"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="25">
         <v>0.05</v>
       </c>
-      <c r="D32" s="25"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="26">
         <f>C10</f>
         <v>6.5242598122280206</v>
       </c>
-      <c r="D33" s="25"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="27">
         <v>44</v>
       </c>
-      <c r="D34" s="25"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="27">
         <v>34</v>
       </c>
-      <c r="D35" s="25"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="27">
         <v>21</v>
       </c>
-      <c r="D36" s="25"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="27">
         <v>15</v>
       </c>
-      <c r="D37" s="25"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="27">
         <v>4</v>
       </c>
-      <c r="D38" s="25"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="23" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="27">
         <v>87540</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="27">
         <v>87540</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="27">
         <f>C42*1.5</f>
         <v>131310</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="27">
         <v>87540</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="25">
         <f>D44</f>
         <v>0.8</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="28">
         <v>0.8</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="29">
         <v>3.3475000000000001</v>
       </c>
-      <c r="D45" s="36">
+      <c r="D45" s="29">
         <v>3.3475000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="37">
+      <c r="C46" s="30">
         <v>5280</v>
       </c>
-      <c r="D46" s="37">
+      <c r="D46" s="30">
         <v>5280</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="30">
         <f>C45*C46</f>
         <v>17674.8</v>
       </c>
-      <c r="D47" s="37">
+      <c r="D47" s="30">
         <f>D45*D46</f>
         <v>17674.8</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="16">
         <f>AVERAGE(C43:D43)/(AVERAGE(C47:D47)*10^6)</f>
         <v>6.1910177201439334E-6</v>
       </c>
@@ -2998,129 +2628,128 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70154B78-0E9B-4A9B-9D3C-65AF6790BABC}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21" style="25" customWidth="1"/>
-    <col min="2" max="3" width="19.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="25" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="3" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="33" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4">
         <v>56603</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="34">
         <v>750000</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <f>C4/(B4*10^6)</f>
         <v>1.3250181085808173E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5">
         <v>25717</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="34">
         <v>700000</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="17">
         <f t="shared" ref="D5:D7" si="0">C5/(B5*10^6)</f>
         <v>2.7219349068709415E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6">
         <v>60507</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="34">
         <v>1250000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="17">
         <f t="shared" si="0"/>
         <v>2.0658766754259837E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7">
         <f>AVERAGE(B4:B6)</f>
         <v>47609</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7">
         <f>AVERAGE(C4:C6)</f>
         <v>900000</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="38">
         <f t="shared" si="0"/>
         <v>1.8903988741624482E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="37">
         <v>0.67400000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="36">
         <f>D7*(1-A15)</f>
         <v>6.1627003297695804E-6</v>
       </c>
@@ -3135,140 +2764,139 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586C6099-D878-4CA6-905E-BCE566C93FAD}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" style="25" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="25" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="25"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
-      <c r="B5" s="25" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+      <c r="B5" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="42"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="C6" s="47"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="C5" s="35"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="12"/>
+      <c r="C6" s="12"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="47"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="40"/>
+      <c r="C7" s="12"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>148</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="47"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="12"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="41">
         <v>50</v>
       </c>
-      <c r="C9" s="47"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="41">
         <v>75</v>
       </c>
-      <c r="C10" s="47"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="C10" s="12"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="52">
+      <c r="B11" s="43">
         <f>AVERAGE(B9:B10)</f>
         <v>62.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>153</v>
       </c>
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>0.47</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <f>24*365</f>
         <v>8760</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>155</v>
       </c>
       <c r="B19" s="10"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="53">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="44">
         <f>B11/(A17*A14)</f>
         <v>1.5180219566695814E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <f>2.93*10^-4</f>
         <v>2.9300000000000002E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>156</v>
       </c>
       <c r="B25" s="8"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="16">
         <f>A20*A23</f>
         <v>4.4478043330418734E-6</v>
       </c>
@@ -3283,1072 +2911,1692 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BB8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="36.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="27">
+      <c r="B1" s="12">
         <v>2018</v>
       </c>
       <c r="C1">
         <v>2019</v>
       </c>
-      <c r="D1" s="27">
+      <c r="D1" s="12">
         <v>2020</v>
       </c>
-      <c r="E1" s="25">
+      <c r="E1">
         <v>2021</v>
       </c>
-      <c r="F1" s="27">
+      <c r="F1" s="12">
         <v>2022</v>
       </c>
-      <c r="G1" s="25">
+      <c r="G1">
         <v>2023</v>
       </c>
-      <c r="H1" s="27">
+      <c r="H1" s="12">
         <v>2024</v>
       </c>
-      <c r="I1" s="25">
+      <c r="I1">
         <v>2025</v>
       </c>
-      <c r="J1" s="27">
+      <c r="J1" s="12">
         <v>2026</v>
       </c>
-      <c r="K1" s="25">
+      <c r="K1">
         <v>2027</v>
       </c>
-      <c r="L1" s="27">
+      <c r="L1" s="12">
         <v>2028</v>
       </c>
-      <c r="M1" s="25">
+      <c r="M1">
         <v>2029</v>
       </c>
-      <c r="N1" s="27">
+      <c r="N1" s="12">
         <v>2030</v>
       </c>
-      <c r="O1" s="25">
+      <c r="O1">
         <v>2031</v>
       </c>
-      <c r="P1" s="27">
+      <c r="P1" s="12">
         <v>2032</v>
       </c>
-      <c r="Q1" s="25">
+      <c r="Q1">
         <v>2033</v>
       </c>
-      <c r="R1" s="27">
+      <c r="R1" s="12">
         <v>2034</v>
       </c>
-      <c r="S1" s="25">
+      <c r="S1">
         <v>2035</v>
       </c>
-      <c r="T1" s="27">
+      <c r="T1" s="12">
         <v>2036</v>
       </c>
-      <c r="U1" s="25">
+      <c r="U1">
         <v>2037</v>
       </c>
-      <c r="V1" s="27">
+      <c r="V1" s="12">
         <v>2038</v>
       </c>
-      <c r="W1" s="25">
+      <c r="W1">
         <v>2039</v>
       </c>
-      <c r="X1" s="27">
+      <c r="X1" s="12">
         <v>2040</v>
       </c>
-      <c r="Y1" s="25">
+      <c r="Y1">
         <v>2041</v>
       </c>
-      <c r="Z1" s="27">
+      <c r="Z1" s="12">
         <v>2042</v>
       </c>
-      <c r="AA1" s="25">
+      <c r="AA1">
         <v>2043</v>
       </c>
-      <c r="AB1" s="27">
+      <c r="AB1" s="12">
         <v>2044</v>
       </c>
-      <c r="AC1" s="25">
+      <c r="AC1">
         <v>2045</v>
       </c>
-      <c r="AD1" s="27">
+      <c r="AD1" s="12">
         <v>2046</v>
       </c>
-      <c r="AE1" s="25">
+      <c r="AE1">
         <v>2047</v>
       </c>
-      <c r="AF1" s="27">
+      <c r="AF1" s="12">
         <v>2048</v>
       </c>
-      <c r="AG1" s="25">
+      <c r="AG1">
         <v>2049</v>
       </c>
-      <c r="AH1" s="27">
+      <c r="AH1" s="12">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1">
+        <v>2051</v>
+      </c>
+      <c r="AJ1">
+        <v>2052</v>
+      </c>
+      <c r="AK1">
+        <v>2053</v>
+      </c>
+      <c r="AL1">
+        <v>2054</v>
+      </c>
+      <c r="AM1">
+        <v>2055</v>
+      </c>
+      <c r="AN1">
+        <v>2056</v>
+      </c>
+      <c r="AO1">
+        <v>2057</v>
+      </c>
+      <c r="AP1">
+        <v>2058</v>
+      </c>
+      <c r="AQ1">
+        <v>2059</v>
+      </c>
+      <c r="AR1">
+        <v>2060</v>
+      </c>
+      <c r="AS1">
+        <v>2061</v>
+      </c>
+      <c r="AT1">
+        <v>2062</v>
+      </c>
+      <c r="AU1">
+        <v>2063</v>
+      </c>
+      <c r="AV1">
+        <v>2064</v>
+      </c>
+      <c r="AW1">
+        <v>2065</v>
+      </c>
+      <c r="AX1">
+        <v>2066</v>
+      </c>
+      <c r="AY1">
+        <v>2067</v>
+      </c>
+      <c r="AZ1">
+        <v>2068</v>
+      </c>
+      <c r="BA1">
+        <v>2069</v>
+      </c>
+      <c r="BB1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="17">
         <f>'early retirement'!A20*About!$A$57</f>
         <v>1.4243732995275992E-4</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="17">
         <f>$B2</f>
         <v>1.4243732995275992E-4</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <f>$B2</f>
         <v>1.4243732995275992E-4</v>
       </c>
-      <c r="E2" s="20">
-        <f t="shared" ref="E2:AH8" si="0">$B2</f>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="F2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="G2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="H2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="I2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="J2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="K2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="L2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="M2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="N2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="O2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="P2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="Q2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="R2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="S2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="T2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="U2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="V2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="W2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="X2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="Y2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="Z2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AA2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AB2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AC2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AD2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AE2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AF2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AG2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-      <c r="AH2" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="E2" s="17">
+        <f t="shared" ref="E2:AI8" si="0">$B2</f>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="F2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="G2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="H2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="I2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="J2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="K2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="L2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="M2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="N2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="O2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="P2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="Q2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="R2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="S2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="T2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="U2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="V2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="W2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="X2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="Y2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="Z2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AA2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AB2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AC2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AD2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AE2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AF2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AG2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AH2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AI2" s="17">
+        <f t="shared" si="0"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AJ2" s="17">
+        <f t="shared" ref="AI2:BB8" si="1">$B2</f>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AK2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AL2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AM2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AN2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AO2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AP2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AQ2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AR2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AS2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AT2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AU2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AV2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AW2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AX2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AY2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="AZ2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="BA2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+      <c r="BB2" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4243732995275992E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3" s="28">
-        <f t="shared" ref="C3:R8" si="1">$B3</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R3" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH3" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <f t="shared" ref="C3:R8" si="2">$B3</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="17">
         <f>'cogen and WHR'!B29*About!$A$58</f>
         <v>2.4092251461988303E-5</v>
       </c>
-      <c r="C4" s="20">
-        <f t="shared" si="1"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="D4" s="20">
-        <f t="shared" si="1"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="E4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="F4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="G4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="H4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="I4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="J4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="K4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="L4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="M4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="N4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="O4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="P4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="Q4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="R4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="S4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="T4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="U4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="V4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="W4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="X4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="Y4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="Z4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AA4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AB4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AC4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AD4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AE4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AF4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AG4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-      <c r="AH4" s="20">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C4" s="17">
+        <f t="shared" si="2"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="D4" s="17">
+        <f t="shared" si="2"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="E4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="G4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="H4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="I4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="J4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="K4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="L4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="M4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="N4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="O4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="P4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="Q4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="R4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="S4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="T4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="U4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="V4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="W4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="X4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="Y4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="Z4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AA4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AB4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AC4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AD4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AE4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AF4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AG4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AH4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AI4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AJ4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AK4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AL4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AM4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AN4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AO4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AP4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AQ4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AR4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AS4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AT4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AU4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AV4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AW4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AX4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AY4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="AZ4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="BA4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+      <c r="BB4" s="17">
+        <f t="shared" si="1"/>
+        <v>2.4092251461988303E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="17">
         <f>efficiency!B5</f>
         <v>5.2772702980209352E-5</v>
       </c>
-      <c r="C5" s="20">
-        <f t="shared" si="1"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="D5" s="20">
-        <f t="shared" si="1"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="E5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="F5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="G5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="H5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="I5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="J5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="K5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="L5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="M5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="N5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="O5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="P5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="Q5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="R5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="S5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="T5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="U5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="V5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="W5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="X5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="Y5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="Z5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AA5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AB5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AC5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AD5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AE5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AF5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AG5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-      <c r="AH5" s="20">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C5" s="17">
+        <f t="shared" si="2"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="D5" s="17">
+        <f t="shared" si="2"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="E5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="G5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="I5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="J5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="K5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="L5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="M5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="N5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="O5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="P5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="Q5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="R5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="S5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="T5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="U5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="W5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="X5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="Y5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="Z5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AA5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AB5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AC5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AD5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AE5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AF5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AG5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AH5" s="17">
+        <f t="shared" si="0"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AI5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AJ5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AK5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AL5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AM5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AN5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AO5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AP5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AQ5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AR5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AS5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AT5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AU5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AV5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AW5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AX5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AY5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="AZ5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="BA5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+      <c r="BB5" s="17">
+        <f t="shared" si="1"/>
+        <v>5.2772702980209352E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="17">
         <f>'med and high temp fuel shifting'!$A$50</f>
         <v>6.1910177201439334E-6</v>
       </c>
-      <c r="C6" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="D6" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="E6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="F6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="G6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="H6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="I6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="J6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="K6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="L6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="M6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="N6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="O6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="P6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="Q6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="R6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="S6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="T6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="U6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="V6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="W6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="X6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="Y6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="Z6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AA6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AB6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AC6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AD6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AE6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AF6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AG6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-      <c r="AH6" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="C6" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="D6" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="E6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="G6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="H6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="I6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="J6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="K6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="L6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="M6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="O6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="P6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="Q6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="R6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="S6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="T6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="U6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="V6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="W6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="X6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="Y6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="Z6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AA6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AB6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AC6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AD6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AE6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AF6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AG6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AH6" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AI6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AJ6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AK6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AL6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AM6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AN6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AO6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AP6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AQ6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AR6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AS6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AT6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AU6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AV6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AW6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AX6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AY6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AZ6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="BA6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="BB6" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="17">
         <f>'low temp fuel type shifting'!A18</f>
         <v>6.1627003297695804E-6</v>
       </c>
-      <c r="C7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="D7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="E7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="F7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="G7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="H7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="I7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="J7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="K7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="L7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="M7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="N7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="O7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="P7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="Q7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="R7" s="20">
-        <f t="shared" si="1"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="S7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="T7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="U7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="V7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="W7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="X7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="Y7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="Z7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AA7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AB7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AC7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AD7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AE7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AF7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AG7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-      <c r="AH7" s="20">
-        <f t="shared" si="0"/>
-        <v>6.1627003297695804E-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="D7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="E7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="H7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="I7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="L7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="M7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="N7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="O7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="P7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="Q7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="R7" s="17">
+        <f t="shared" si="2"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="S7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="T7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="U7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="V7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="W7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="X7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="Y7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="Z7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AA7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AB7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AC7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AD7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AE7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AF7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AG7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AH7" s="17">
+        <f t="shared" si="0"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AI7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AJ7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AK7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AL7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AM7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AN7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AO7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AP7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AQ7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AR7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AS7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AT7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AU7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AV7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AW7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AX7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AY7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="AZ7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="BA7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+      <c r="BB7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1627003297695804E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="20">
-        <v>0</v>
-      </c>
-      <c r="C8" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D8" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG8" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH8" s="28">
-        <f t="shared" si="0"/>
+      <c r="B8" s="17">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
